--- a/input/PL/EUROMODpolicySchedule.xlsx
+++ b/input/PL/EUROMODpolicySchedule.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="77">
   <si>
     <t>Filename</t>
   </si>
@@ -608,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FED923-16BB-49A3-BC38-F01A901092C1}">
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="17.85546875" collapsed="true"/>
@@ -631,13 +631,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -645,13 +645,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -659,13 +659,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -673,13 +673,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -687,13 +687,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -701,13 +701,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
@@ -715,13 +715,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
@@ -729,13 +729,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
@@ -743,13 +743,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
@@ -757,13 +757,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -771,13 +771,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
         <v>13</v>
@@ -785,13 +785,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
@@ -799,13 +799,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
         <v>13</v>
@@ -813,631 +813,15 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>54</v>
-      </c>
-      <c r="B29" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>24</v>
-      </c>
-      <c r="B32" t="s">
-        <v>4</v>
-      </c>
-      <c r="C32" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>57</v>
-      </c>
-      <c r="B33" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>28</v>
-      </c>
-      <c r="B34" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>58</v>
-      </c>
-      <c r="B35" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>59</v>
-      </c>
-      <c r="B36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>29</v>
-      </c>
-      <c r="B37" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>60</v>
-      </c>
-      <c r="B38" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>61</v>
-      </c>
-      <c r="B39" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" t="s">
-        <v>13</v>
-      </c>
-      <c r="D39" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>62</v>
-      </c>
-      <c r="B40" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>63</v>
-      </c>
-      <c r="B41" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>64</v>
-      </c>
-      <c r="B42" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>25</v>
-      </c>
-      <c r="B43" t="s">
-        <v>5</v>
-      </c>
-      <c r="C43" t="s">
-        <v>5</v>
-      </c>
-      <c r="D43" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>65</v>
-      </c>
-      <c r="B44" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>66</v>
-      </c>
-      <c r="B45" t="s">
-        <v>13</v>
-      </c>
-      <c r="C45" t="s">
-        <v>13</v>
-      </c>
-      <c r="D45" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>67</v>
-      </c>
-      <c r="B46" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>31</v>
-      </c>
-      <c r="B47" t="s">
-        <v>17</v>
-      </c>
-      <c r="C47" t="s">
-        <v>17</v>
-      </c>
-      <c r="D47" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>68</v>
-      </c>
-      <c r="B48" t="s">
-        <v>13</v>
-      </c>
-      <c r="C48" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>69</v>
-      </c>
-      <c r="B49" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>23</v>
-      </c>
-      <c r="B50" t="s">
-        <v>3</v>
-      </c>
-      <c r="C50" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>70</v>
-      </c>
-      <c r="B51" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" t="s">
-        <v>13</v>
-      </c>
-      <c r="D51" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>71</v>
-      </c>
-      <c r="B52" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>22</v>
-      </c>
-      <c r="B53" t="s">
-        <v>11</v>
-      </c>
-      <c r="C53" t="s">
-        <v>11</v>
-      </c>
-      <c r="D53" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>72</v>
-      </c>
-      <c r="B54" t="s">
-        <v>13</v>
-      </c>
-      <c r="C54" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>73</v>
-      </c>
-      <c r="B55" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" t="s">
-        <v>13</v>
-      </c>
-      <c r="D55" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>74</v>
-      </c>
-      <c r="B56" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" t="s">
-        <v>13</v>
-      </c>
-      <c r="D56" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>30</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="s">
-        <v>16</v>
-      </c>
-      <c r="D57" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>75</v>
-      </c>
-      <c r="B58" t="s">
-        <v>13</v>
-      </c>
-      <c r="C58" t="s">
-        <v>13</v>
-      </c>
-      <c r="D58" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>76</v>
-      </c>
-      <c r="B59" t="s">
-        <v>13</v>
-      </c>
-      <c r="C59" t="s">
-        <v>13</v>
-      </c>
-      <c r="D59" t="s">
         <v>13</v>
       </c>
     </row>

--- a/input/PL/EUROMODpolicySchedule.xlsx
+++ b/input/PL/EUROMODpolicySchedule.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="77">
   <si>
     <t>Filename</t>
   </si>
